--- a/update-ml-labreport-laboratoryobservation/ig/StructureDefinition-FRLMCorpsDocument.xlsx
+++ b/update-ml-labreport-laboratoryobservation/ig/StructureDefinition-FRLMCorpsDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:28:49+00:00</t>
+    <t>2026-09-16T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,24 +567,14 @@
     <t>Section Exposition aux radiations</t>
   </si>
   <si>
-    <t>FRLMCorpsDocument.imagingSupportingInformation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMImagingSupportingInformation
+    <t>FRLMCorpsDocument.supportingInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSupportingInformation
 </t>
   </si>
   <si>
-    <t>Section Informations cliniques (imagerie)</t>
-  </si>
-  <si>
-    <t>FRLMCorpsDocument.laboratorySupportingInformation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratorySupportingInformation
-</t>
-  </si>
-  <si>
-    <t>Section Informations cliniques (biologie)</t>
+    <t>Section Informations cliniques</t>
   </si>
   <si>
     <t>FRLMCorpsDocument.dicomStudyMetadata</t>
@@ -976,7 +966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ45"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.14453125" customWidth="true" bestFit="true"/>
@@ -989,7 +979,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="85.0703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.7265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5426,106 +5416,6 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
